--- a/docs/01_設計/05_API設計書.xlsx
+++ b/docs/01_設計/05_API設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Documents/projects/task-manager-app/docs/01_設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE287BF-5C3E-3D4C-9555-7D2D10AEDCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700724E8-D341-834E-A507-384806266003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API一覧" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="378">
   <si>
     <t>API設計書 概要</t>
   </si>
@@ -123,7 +123,7 @@
     <t>最優先API</t>
   </si>
   <si>
-    <t>認証 / タスク</t>
+    <t>認証 / タスク / ユーザー候補取得</t>
   </si>
   <si>
     <t>HTTP</t>
@@ -135,7 +135,7 @@
     <t>補足</t>
   </si>
   <si>
-    <t>MVPは認証とタスクCRUDを優先実装</t>
+    <t>MVPは認証とタスクCRUD、および担当者候補取得を優先実装</t>
   </si>
   <si>
     <t>参考</t>
@@ -267,9 +267,6 @@
     <t>タスク作成画面</t>
   </si>
   <si>
-    <t>作成者は認証ユーザー</t>
-  </si>
-  <si>
     <t>タスク更新</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>タスク編集画面</t>
   </si>
   <si>
-    <t>編集画面は作成画面と同一フォーム構成</t>
-  </si>
-  <si>
     <t>タスク削除</t>
   </si>
   <si>
@@ -1122,9 +1116,6 @@
     <t>PUT /api/tasks/{taskId} タスク更新</t>
   </si>
   <si>
-    <t>担当者ユーザーID（任意）</t>
-  </si>
-  <si>
     <t>{"title":"API設計書を更新する","description":"レスポンス例とエラー設計を追加する","status":"DOING","priority":"HIGH","dueDate":"2026-04-13","assignedUserId":1,"teamId":null}</t>
   </si>
   <si>
@@ -1171,6 +1162,63 @@
   </si>
   <si>
     <t>ロール更新</t>
+  </si>
+  <si>
+    <t>作成者は認証ユーザー。担当者候補は GET /api/users で取得</t>
+  </si>
+  <si>
+    <t>編集画面は作成画面と同一フォーム構成。担当者候補は GET /api/users で取得</t>
+  </si>
+  <si>
+    <t>ユーザー</t>
+  </si>
+  <si>
+    <t>担当者候補一覧取得</t>
+  </si>
+  <si>
+    <t>/api/users</t>
+  </si>
+  <si>
+    <t>担当者候補一覧を取得する</t>
+  </si>
+  <si>
+    <t>タスク作成画面 / タスク編集画面</t>
+  </si>
+  <si>
+    <t>担当者プルダウン表示用</t>
+  </si>
+  <si>
+    <t>担当者ユーザーID（任意）。フォームでは GET /api/users の候補から選択</t>
+  </si>
+  <si>
+    <t>GET /api/users 担当者候補一覧取得</t>
+  </si>
+  <si>
+    <t>担当者プルダウン表示用の候補一覧を取得する</t>
+  </si>
+  <si>
+    <t>認証済みユーザーを候補として返却する</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>担当者候補を全件返却する</t>
+  </si>
+  <si>
+    <t>[].name</t>
+  </si>
+  <si>
+    <t>[].email</t>
+  </si>
+  <si>
+    <t>[{"id":1,"name":"佐伯将伍","email":"test@example.com"},{"id":2,"name":"田中花子","email":"hanako@example.com"}]</t>
+  </si>
+  <si>
+    <t>担当者候補一覧の取得に失敗しました</t>
   </si>
 </sst>
 </file>
@@ -1396,16 +1444,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1708,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1997,7 +2045,7 @@
         <v>59</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>60</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
@@ -2005,10 +2053,10 @@
         <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>53</v>
@@ -2017,16 +2065,16 @@
         <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>65</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
@@ -2034,10 +2082,10 @@
         <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>53</v>
@@ -2046,7 +2094,7 @@
         <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>36</v>
@@ -2055,413 +2103,442 @@
         <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2566,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2506,18 +2583,18 @@
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>47</v>
@@ -2525,63 +2602,63 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -2589,13 +2666,13 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
@@ -2606,13 +2683,13 @@
         <v>200</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
@@ -2620,10 +2697,10 @@
         <v>201</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>32</v>
@@ -2634,13 +2711,13 @@
         <v>204</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
@@ -2648,13 +2725,13 @@
         <v>400</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -2662,13 +2739,13 @@
         <v>401</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
@@ -2676,13 +2753,13 @@
         <v>403</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -2690,13 +2767,13 @@
         <v>404</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -2704,13 +2781,13 @@
         <v>409</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -2718,18 +2795,18 @@
         <v>500</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
       <c r="A21" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2740,80 +2817,80 @@
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>47</v>
@@ -2821,7 +2898,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2829,7 +2906,7 @@
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2837,72 +2914,72 @@
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B32" s="15">
         <v>401</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B33" s="15">
         <v>401</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B34" s="15">
         <v>401</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B35" s="15">
         <v>403</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1">
@@ -2913,7 +2990,7 @@
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -2921,13 +2998,13 @@
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
       <c r="A38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>30</v>
@@ -2935,44 +3012,44 @@
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1">
       <c r="A39" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>208</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>211</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
       <c r="A41" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
@@ -3010,7 +3087,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3040,7 +3117,7 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -3052,7 +3129,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>37</v>
@@ -3066,10 +3143,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
@@ -3080,7 +3157,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -3088,63 +3165,63 @@
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -3152,7 +3229,7 @@
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -3160,13 +3237,13 @@
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
@@ -3174,59 +3251,59 @@
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -3234,7 +3311,7 @@
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1">
       <c r="A21" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -3242,77 +3319,77 @@
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -3342,7 +3419,7 @@
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3354,7 +3431,7 @@
         <v>34</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>42</v>
@@ -3368,21 +3445,21 @@
         <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1">
       <c r="A34" s="17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -3390,49 +3467,49 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -3440,7 +3517,7 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -3448,13 +3525,13 @@
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>30</v>
@@ -3462,57 +3539,57 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -3520,7 +3597,7 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -3528,44 +3605,44 @@
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="36" customHeight="1">
@@ -3573,23 +3650,23 @@
         <v>15</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E52" s="16"/>
       <c r="F52" s="16"/>
     </row>
     <row r="53" spans="1:6" ht="36" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
@@ -3618,29 +3695,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.5" bestFit="1" customWidth="1"/>
     <col min="7" max="26" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
+    <row r="1" spans="1:6" ht="16" thickBot="1">
+      <c r="A1" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3660,9 +3737,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1">
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
@@ -3674,332 +3751,335 @@
         <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
+    <row r="4" spans="1:6" ht="30">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1"/>
+    <row r="6" spans="1:6" ht="16" thickBot="1">
+      <c r="A6" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="15">
       <c r="A7" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
       <c r="A9" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
       <c r="A10" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
       <c r="A11" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1"/>
+    <row r="13" spans="1:6" ht="16" thickBot="1">
+      <c r="A13" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="15">
       <c r="A14" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1">
+    <row r="15" spans="1:6" ht="15">
       <c r="A15" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
+      <c r="B18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1">
+    <row r="24" spans="1:6" ht="15" thickBot="1"/>
+    <row r="25" spans="1:6" ht="16" thickBot="1">
+      <c r="A25" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" ht="15">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
       <c r="A27" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="34" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
       <c r="A28" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D28" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6" ht="34" customHeight="1">
+    <row r="29" spans="1:6" ht="15">
       <c r="A29" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1"/>
+    <row r="33" spans="1:6" ht="16" thickBot="1">
+      <c r="A33" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1">
-      <c r="A31" s="26"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1"/>
-    <row r="33" spans="1:6" ht="15" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -4007,7 +4087,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1">
+    <row r="34" spans="1:6" ht="15">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -4029,7 +4109,7 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>52</v>
@@ -4041,13 +4121,13 @@
         <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1">
+    <row r="36" spans="1:6" ht="15">
       <c r="A36" s="25" t="s">
         <v>27</v>
       </c>
@@ -4058,161 +4138,161 @@
         <v>30</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1"/>
-    <row r="38" spans="1:6" ht="15" customHeight="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" thickBot="1"/>
+    <row r="38" spans="1:6" ht="16" thickBot="1">
       <c r="A38" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1">
+    <row r="39" spans="1:6" ht="15">
       <c r="A39" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1">
+    <row r="40" spans="1:6" ht="15">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1">
-      <c r="A42" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1">
-      <c r="A45" s="3" t="s">
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B46" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1">
-      <c r="A48" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="B49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="23" t="s">
-        <v>239</v>
+      <c r="A50" s="24" t="s">
+        <v>237</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -4220,114 +4300,113 @@
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="22"/>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1"/>
-    <row r="54" spans="1:6" ht="15" customHeight="1">
+    <row r="53" spans="1:6" ht="15" thickBot="1"/>
+    <row r="54" spans="1:6" ht="16" thickBot="1">
       <c r="A54" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="1:6" ht="34" customHeight="1">
+    <row r="55" spans="1:6" ht="15">
       <c r="A55" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="34" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15">
       <c r="A56" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="30">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15">
       <c r="A57" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B57" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D57" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
     </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1">
+    <row r="58" spans="1:6" ht="15">
       <c r="A58" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1">
+    <row r="59" spans="1:6" ht="15">
       <c r="A59" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1"/>
+    <row r="62" spans="1:6" ht="16" thickBot="1">
+      <c r="A62" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1"/>
-    <row r="61" spans="1:6" ht="30" customHeight="1"/>
-    <row r="62" spans="1:6" ht="15">
-      <c r="A62" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -4335,8 +4414,8 @@
       <c r="E62" s="7"/>
       <c r="F62" s="11"/>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1">
-      <c r="A63" s="24" t="s">
+    <row r="63" spans="1:6" ht="15">
+      <c r="A63" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B63" s="21"/>
@@ -4349,9 +4428,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1">
+    <row r="64" spans="1:6" ht="15">
       <c r="A64" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>57</v>
@@ -4363,98 +4442,97 @@
         <v>48</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" customHeight="1">
+    <row r="65" spans="1:6" ht="15">
       <c r="A65" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15" customHeight="1"/>
-    <row r="67" spans="1:6" ht="15" customHeight="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15">
       <c r="A67" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="1:6" ht="15" customHeight="1">
+    <row r="68" spans="1:6" ht="15">
       <c r="A68" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15" customHeight="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15">
       <c r="A69" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" customHeight="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15">
       <c r="A70" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15" customHeight="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15">
       <c r="A71" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="23" t="s">
-        <v>284</v>
+      <c r="A72" s="24" t="s">
+        <v>282</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="21"/>
@@ -4462,142 +4540,143 @@
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15" customHeight="1">
-      <c r="A74" s="23" t="s">
-        <v>286</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="24" t="s">
+        <v>284</v>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="21"/>
-      <c r="D74" s="22"/>
-    </row>
-    <row r="75" spans="1:6" ht="15" customHeight="1">
+      <c r="D74" s="22" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15">
       <c r="A75" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15" customHeight="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="90">
       <c r="A76" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="10"/>
     </row>
-    <row r="77" spans="1:6" ht="15" customHeight="1"/>
-    <row r="78" spans="1:6" ht="15" customHeight="1">
+    <row r="78" spans="1:6" ht="15">
       <c r="A78" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="1:6" ht="15" customHeight="1">
+    <row r="79" spans="1:6" ht="15">
       <c r="A79" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15" customHeight="1">
+    <row r="80" spans="1:6" ht="15">
       <c r="A80" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D80" s="3"/>
+    </row>
+    <row r="81" spans="1:6" ht="15">
+      <c r="A81" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D80" s="3"/>
-    </row>
-    <row r="81" spans="1:6" ht="15" customHeight="1">
-      <c r="A81" s="3" t="s">
+      <c r="D81" s="3"/>
+    </row>
+    <row r="82" spans="1:6" ht="15">
+      <c r="A82" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:6" ht="15">
+      <c r="A83" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" s="3"/>
+    </row>
+    <row r="84" spans="1:6" ht="15">
+      <c r="A84" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D84" s="3"/>
+    </row>
+    <row r="85" spans="1:6" ht="15">
+      <c r="A85" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D81" s="3"/>
-    </row>
-    <row r="82" spans="1:6" ht="15" customHeight="1">
-      <c r="A82" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D82" s="3"/>
-    </row>
-    <row r="83" spans="1:6" ht="15" customHeight="1">
-      <c r="A83" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D83" s="3"/>
-    </row>
-    <row r="84" spans="1:6" ht="15" customHeight="1">
-      <c r="A84" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="B85" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D84" s="3"/>
-    </row>
-    <row r="85" spans="1:6" ht="15" customHeight="1">
-      <c r="A85" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="D85" s="3"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="23" t="s">
-        <v>324</v>
+      <c r="A86" s="24" t="s">
+        <v>322</v>
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="21"/>
@@ -4605,102 +4684,101 @@
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15" customHeight="1">
-      <c r="A88" s="23" t="s">
-        <v>239</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="24" t="s">
+        <v>237</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
       <c r="D88" s="22"/>
     </row>
-    <row r="89" spans="1:6" ht="15" customHeight="1">
+    <row r="89" spans="1:6" ht="15">
       <c r="A89" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="135">
       <c r="A90" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="10"/>
     </row>
-    <row r="91" spans="1:6" ht="30" customHeight="1"/>
-    <row r="92" spans="1:6" ht="15" customHeight="1">
+    <row r="92" spans="1:6" ht="15">
       <c r="A92" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="11"/>
     </row>
-    <row r="93" spans="1:6" ht="15" customHeight="1">
+    <row r="93" spans="1:6" ht="15">
       <c r="A93" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15">
+      <c r="A94" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="34" customHeight="1">
-      <c r="A94" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="B94" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15">
+      <c r="A95" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="34" customHeight="1">
-      <c r="A95" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="15" customHeight="1">
-      <c r="A96" s="23" t="s">
-        <v>245</v>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="24" t="s">
+        <v>243</v>
       </c>
       <c r="B96" s="21"/>
       <c r="C96" s="21"/>
@@ -4708,61 +4786,61 @@
       <c r="E96" s="21"/>
       <c r="F96" s="22"/>
     </row>
-    <row r="97" spans="1:6" ht="15" customHeight="1">
+    <row r="97" spans="1:6" ht="15">
       <c r="A97" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15">
       <c r="A98" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C98" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D98" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
     </row>
-    <row r="99" spans="1:6" ht="30" customHeight="1">
+    <row r="99" spans="1:6" ht="15">
       <c r="A99" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D99" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="B99" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="E99" s="16"/>
       <c r="F99" s="16"/>
     </row>
-    <row r="101" spans="1:6" ht="15" customHeight="1">
-      <c r="A101" s="26"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="26"/>
-    </row>
-    <row r="102" spans="1:6" ht="15" customHeight="1">
+    <row r="101" spans="1:6">
+      <c r="A101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23"/>
+    </row>
+    <row r="102" spans="1:6" ht="15">
       <c r="A102" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -4770,7 +4848,7 @@
       <c r="E102" s="7"/>
       <c r="F102" s="11"/>
     </row>
-    <row r="103" spans="1:6" ht="15" customHeight="1">
+    <row r="103" spans="1:6" ht="15">
       <c r="A103" s="1" t="s">
         <v>1</v>
       </c>
@@ -4790,12 +4868,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15" customHeight="1">
+    <row r="104" spans="1:6" ht="15">
       <c r="A104" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>26</v>
@@ -4804,72 +4882,71 @@
         <v>48</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15" customHeight="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15">
       <c r="A105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15" customHeight="1"/>
-    <row r="107" spans="1:6" ht="15" customHeight="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15">
       <c r="A107" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
     </row>
-    <row r="108" spans="1:6" ht="15" customHeight="1">
+    <row r="108" spans="1:6" ht="15">
       <c r="A108" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="15" customHeight="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15">
       <c r="A109" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="23" t="s">
-        <v>317</v>
+      <c r="A110" s="24" t="s">
+        <v>315</v>
       </c>
       <c r="B110" s="21"/>
       <c r="C110" s="21"/>
@@ -4877,144 +4954,143 @@
     </row>
     <row r="111" spans="1:6" ht="15">
       <c r="A111" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" customHeight="1">
-      <c r="A112" s="23" t="s">
-        <v>284</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="24" t="s">
+        <v>282</v>
       </c>
       <c r="B112" s="21"/>
       <c r="C112" s="21"/>
       <c r="D112" s="22"/>
     </row>
-    <row r="113" spans="1:4" ht="15" customHeight="1">
+    <row r="113" spans="1:4" ht="15">
       <c r="A113" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="15" customHeight="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15">
       <c r="A114" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15" customHeight="1">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15">
       <c r="A115" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15" customHeight="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="90">
       <c r="A116" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="10"/>
     </row>
-    <row r="117" spans="1:4" ht="15" customHeight="1"/>
-    <row r="118" spans="1:4" ht="15" customHeight="1">
+    <row r="118" spans="1:4" ht="15">
       <c r="A118" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
       <c r="D118" s="11"/>
     </row>
-    <row r="119" spans="1:4" ht="15" customHeight="1">
+    <row r="119" spans="1:4" ht="15">
       <c r="A119" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15" customHeight="1">
+    <row r="120" spans="1:4" ht="15">
       <c r="A120" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D120" s="3"/>
+    </row>
+    <row r="121" spans="1:4" ht="15">
+      <c r="A121" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D120" s="3"/>
-    </row>
-    <row r="121" spans="1:4" ht="15" customHeight="1">
-      <c r="A121" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B121" s="3" t="s">
+      <c r="D121" s="3"/>
+    </row>
+    <row r="122" spans="1:4" ht="15">
+      <c r="A122" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D122" s="3"/>
+    </row>
+    <row r="123" spans="1:4" ht="15">
+      <c r="A123" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D121" s="3"/>
-    </row>
-    <row r="122" spans="1:4" ht="15" customHeight="1">
-      <c r="A122" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D122" s="3"/>
-    </row>
-    <row r="123" spans="1:4" ht="15" customHeight="1">
-      <c r="A123" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="B123" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D123" s="3"/>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="23" t="s">
-        <v>284</v>
+      <c r="A124" s="24" t="s">
+        <v>282</v>
       </c>
       <c r="B124" s="21"/>
       <c r="C124" s="21"/>
@@ -5022,86 +5098,86 @@
     </row>
     <row r="125" spans="1:4" ht="15">
       <c r="A125" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" ht="15" customHeight="1">
-      <c r="A126" s="23" t="s">
-        <v>324</v>
+    <row r="126" spans="1:4">
+      <c r="A126" s="24" t="s">
+        <v>322</v>
       </c>
       <c r="B126" s="21"/>
       <c r="C126" s="21"/>
       <c r="D126" s="22"/>
     </row>
-    <row r="127" spans="1:4" ht="15" customHeight="1">
+    <row r="127" spans="1:4" ht="15">
       <c r="A127" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C127" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15">
+      <c r="A128" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15">
+      <c r="A129" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="15" customHeight="1">
-      <c r="A128" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="15" customHeight="1">
-      <c r="A129" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="D129" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="34" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="135">
       <c r="A130" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="10"/>
     </row>
-    <row r="131" spans="1:6" ht="34" customHeight="1"/>
-    <row r="132" spans="1:6" ht="15">
+    <row r="131" spans="1:6" ht="15" thickBot="1"/>
+    <row r="132" spans="1:6" ht="16" thickBot="1">
       <c r="A132" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="11"/>
     </row>
-    <row r="133" spans="1:6" ht="15" customHeight="1">
-      <c r="A133" s="24" t="s">
-        <v>243</v>
+    <row r="133" spans="1:6">
+      <c r="A133" s="26" t="s">
+        <v>241</v>
       </c>
       <c r="B133" s="21"/>
       <c r="C133" s="21"/>
@@ -5109,79 +5185,78 @@
       <c r="E133" s="21"/>
       <c r="F133" s="22"/>
     </row>
-    <row r="134" spans="1:6" ht="15" customHeight="1">
+    <row r="134" spans="1:6" ht="15">
       <c r="A134" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="15" customHeight="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="15">
       <c r="A135" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D135" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="30" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="15">
       <c r="A136" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C136" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C136" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D136" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E136" s="16"/>
       <c r="F136" s="16"/>
     </row>
-    <row r="137" spans="1:6" ht="30">
+    <row r="137" spans="1:6" ht="15">
       <c r="A137" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D137" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="B137" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="E137" s="16"/>
       <c r="F137" s="16"/>
     </row>
-    <row r="138" spans="1:6" ht="15" customHeight="1">
-      <c r="A138" s="23" t="s">
-        <v>252</v>
+    <row r="138" spans="1:6">
+      <c r="A138" s="24" t="s">
+        <v>250</v>
       </c>
       <c r="B138" s="21"/>
       <c r="C138" s="21"/>
       <c r="D138" s="22"/>
     </row>
-    <row r="139" spans="1:6" ht="15" customHeight="1"/>
-    <row r="140" spans="1:6" ht="15" customHeight="1"/>
-    <row r="141" spans="1:6" ht="34" customHeight="1">
+    <row r="140" spans="1:6" ht="15" thickBot="1"/>
+    <row r="141" spans="1:6" ht="16" thickBot="1">
       <c r="A141" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -5189,7 +5264,7 @@
       <c r="E141" s="7"/>
       <c r="F141" s="11"/>
     </row>
-    <row r="142" spans="1:6" ht="34" customHeight="1">
+    <row r="142" spans="1:6" ht="15">
       <c r="A142" s="1" t="s">
         <v>1</v>
       </c>
@@ -5211,10 +5286,10 @@
     </row>
     <row r="143" spans="1:6" ht="15">
       <c r="A143" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>26</v>
@@ -5223,35 +5298,35 @@
         <v>48</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="30">
+    <row r="144" spans="1:6" ht="15">
       <c r="A144" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="15">
       <c r="A146" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -5259,93 +5334,326 @@
     </row>
     <row r="147" spans="1:6" ht="15">
       <c r="A147" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="15">
       <c r="A148" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D148" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="30">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15">
       <c r="A149" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C149" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B149" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C149" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D149" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E149" s="16"/>
       <c r="F149" s="16"/>
     </row>
-    <row r="150" spans="1:6" ht="30">
+    <row r="150" spans="1:6" ht="15">
       <c r="A150" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C150" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D150" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="B150" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="C150" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="E150" s="16"/>
       <c r="F150" s="16"/>
     </row>
     <row r="151" spans="1:6" ht="15">
       <c r="A151" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="15" thickBot="1"/>
+    <row r="153" spans="1:6" ht="16" thickBot="1">
+      <c r="A153" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="11"/>
+    </row>
+    <row r="154" spans="1:6" ht="15">
+      <c r="A154" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="15">
+      <c r="A155" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="30">
+      <c r="A156" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="15" thickBot="1"/>
+    <row r="158" spans="1:6" ht="16" thickBot="1">
+      <c r="A158" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+    </row>
+    <row r="159" spans="1:6" ht="15">
+      <c r="A159" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="B160" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="D160" s="24" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="15" thickBot="1"/>
+    <row r="162" spans="1:6" ht="16" thickBot="1">
+      <c r="A162" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+    </row>
+    <row r="163" spans="1:6" ht="15">
+      <c r="A163" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15">
+      <c r="A164" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" spans="1:6" ht="15">
+      <c r="A165" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="15">
+      <c r="A166" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D166" s="3"/>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="B167" s="21"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="22"/>
+    </row>
+    <row r="168" spans="1:6" ht="15" thickBot="1"/>
+    <row r="169" spans="1:6" ht="16" thickBot="1">
+      <c r="A169" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+    </row>
+    <row r="170" spans="1:6" ht="15">
+      <c r="A170" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="15">
+      <c r="A171" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="15">
+      <c r="A172" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B172" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C172" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D172" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E172" s="16"/>
+      <c r="F172" s="16"/>
+    </row>
+    <row r="173" spans="1:6" ht="15">
+      <c r="A173" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A36:D36"/>
+  <mergeCells count="20">
+    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A167:D167"/>
     <mergeCell ref="A138:D138"/>
     <mergeCell ref="A110:D110"/>
     <mergeCell ref="A23:D23"/>
@@ -5355,6 +5663,15 @@
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A112:D112"/>
     <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A88:D88"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5379,7 +5696,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5403,7 +5720,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>26</v>
@@ -5412,21 +5729,21 @@
         <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>55</v>
@@ -5435,24 +5752,24 @@
         <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>55</v>
@@ -5461,24 +5778,24 @@
         <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
@@ -5487,24 +5804,24 @@
         <v>48</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>55</v>
@@ -5513,24 +5830,24 @@
         <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>55</v>
@@ -5539,24 +5856,24 @@
         <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>55</v>
@@ -5565,24 +5882,24 @@
         <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>55</v>
@@ -5591,24 +5908,24 @@
         <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>55</v>
@@ -5618,151 +5935,151 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/docs/01_設計/05_API設計書.xlsx
+++ b/docs/01_設計/05_API設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Documents/projects/task-manager-app/docs/01_設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700724E8-D341-834E-A507-384806266003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB790E7B-47A6-DD48-A6D2-A2FAE69D24D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="共通仕様" sheetId="2" r:id="rId2"/>
     <sheet name="認証API" sheetId="3" r:id="rId3"/>
     <sheet name="タスクAPI" sheetId="4" r:id="rId4"/>
-    <sheet name="拡張API" sheetId="5" r:id="rId5"/>
+    <sheet name="補助・拡張API" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="400">
   <si>
     <t>API設計書 概要</t>
   </si>
@@ -117,15 +117,9 @@
     <t>対象範囲</t>
   </si>
   <si>
-    <t>MVP + 将来拡張API</t>
-  </si>
-  <si>
     <t>最優先API</t>
   </si>
   <si>
-    <t>認証 / タスク / ユーザー候補取得</t>
-  </si>
-  <si>
     <t>HTTP</t>
   </si>
   <si>
@@ -135,9 +129,6 @@
     <t>補足</t>
   </si>
   <si>
-    <t>MVPは認証とタスクCRUD、および担当者候補取得を優先実装</t>
-  </si>
-  <si>
     <t>参考</t>
   </si>
   <si>
@@ -216,9 +207,6 @@
     <t>ログイン画面</t>
   </si>
   <si>
-    <t>成功時にtoken返却</t>
-  </si>
-  <si>
     <t>タスク</t>
   </si>
   <si>
@@ -234,15 +222,9 @@
     <t>要</t>
   </si>
   <si>
-    <t>タスク一覧を取得する</t>
-  </si>
-  <si>
     <t>タスク一覧画面</t>
   </si>
   <si>
-    <t>将来は条件検索対応</t>
-  </si>
-  <si>
     <t>タスク詳細取得</t>
   </si>
   <si>
@@ -255,9 +237,6 @@
     <t>タスク詳細画面</t>
   </si>
   <si>
-    <t>コメント・添付は別APIでも可</t>
-  </si>
-  <si>
     <t>タスク作成</t>
   </si>
   <si>
@@ -288,51 +267,21 @@
     <t>タスクを削除する</t>
   </si>
   <si>
-    <t>成功時204</t>
-  </si>
-  <si>
     <t>コメント</t>
   </si>
   <si>
-    <t>コメント一覧取得</t>
-  </si>
-  <si>
-    <t>/api/tasks/{taskId}/comments</t>
-  </si>
-  <si>
-    <t>対象タスクのコメント一覧を取得する</t>
-  </si>
-  <si>
-    <t>△</t>
-  </si>
-  <si>
-    <t>将来拡張</t>
-  </si>
-  <si>
-    <t>コメント投稿</t>
-  </si>
-  <si>
-    <t>対象タスクにコメントを投稿する</t>
-  </si>
-  <si>
     <t>コメント更新</t>
   </si>
   <si>
     <t>/api/comments/{commentId}</t>
   </si>
   <si>
-    <t>コメントを更新する</t>
-  </si>
-  <si>
     <t>自分のコメントのみ</t>
   </si>
   <si>
     <t>コメント削除</t>
   </si>
   <si>
-    <t>コメントを削除する</t>
-  </si>
-  <si>
     <t>添付</t>
   </si>
   <si>
@@ -342,36 +291,21 @@
     <t>/api/tasks/{taskId}/attachments</t>
   </si>
   <si>
-    <t>添付ファイル一覧を取得する</t>
-  </si>
-  <si>
     <t>添付アップロード</t>
   </si>
   <si>
-    <t>添付ファイルを登録する</t>
-  </si>
-  <si>
-    <t>multipart/form-data想定</t>
-  </si>
-  <si>
     <t>添付ダウンロード</t>
   </si>
   <si>
     <t>/api/attachments/{attachmentId}/download</t>
   </si>
   <si>
-    <t>添付ファイルをダウンロードする</t>
-  </si>
-  <si>
     <t>添付削除</t>
   </si>
   <si>
     <t>/api/attachments/{attachmentId}</t>
   </si>
   <si>
-    <t>添付ファイルを削除する</t>
-  </si>
-  <si>
     <t>チーム</t>
   </si>
   <si>
@@ -381,9 +315,6 @@
     <t>/api/teams</t>
   </si>
   <si>
-    <t>チーム一覧を取得する</t>
-  </si>
-  <si>
     <t>チーム一覧画面</t>
   </si>
   <si>
@@ -393,18 +324,12 @@
     <t>/api/teams/{teamId}</t>
   </si>
   <si>
-    <t>チーム詳細を取得する</t>
-  </si>
-  <si>
     <t>チーム詳細画面</t>
   </si>
   <si>
     <t>チーム作成</t>
   </si>
   <si>
-    <t>新規チームを作成する</t>
-  </si>
-  <si>
     <t>チーム作成相当</t>
   </si>
   <si>
@@ -414,30 +339,18 @@
     <t>/api/teams/{teamId}/members</t>
   </si>
   <si>
-    <t>チームにメンバーを追加する</t>
-  </si>
-  <si>
     <t>メンバー招待画面</t>
   </si>
   <si>
-    <t>メンバー権限更新</t>
-  </si>
-  <si>
     <t>/api/teams/{teamId}/members/{userId}</t>
   </si>
   <si>
-    <t>ロールを更新する</t>
-  </si>
-  <si>
     <t>ロール管理画面</t>
   </si>
   <si>
     <t>メンバー削除</t>
   </si>
   <si>
-    <t>メンバーを外す</t>
-  </si>
-  <si>
     <t>共通仕様</t>
   </si>
   <si>
@@ -447,12 +360,6 @@
     <t>Base URL</t>
   </si>
   <si>
-    <t>/api</t>
-  </si>
-  <si>
-    <t>相対パスで記載</t>
-  </si>
-  <si>
     <t>認証ヘッダ</t>
   </si>
   <si>
@@ -471,18 +378,12 @@
     <t>application/json</t>
   </si>
   <si>
-    <t>添付アップロードのみ multipart/form-data</t>
-  </si>
-  <si>
     <t>日時形式</t>
   </si>
   <si>
     <t>ISO-8601</t>
   </si>
   <si>
-    <t>レスポンスの createdAt / updatedAt など</t>
-  </si>
-  <si>
     <t>2026-04-03T12:00:00</t>
   </si>
   <si>
@@ -555,9 +456,6 @@
     <t>権限なし</t>
   </si>
   <si>
-    <t>他人のコメント編集など</t>
-  </si>
-  <si>
     <t>Not Found</t>
   </si>
   <si>
@@ -618,12 +516,6 @@
     <t>400</t>
   </si>
   <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>HTTPステータス名</t>
-  </si>
-  <si>
     <t>message</t>
   </si>
   <si>
@@ -639,9 +531,6 @@
     <t>リクエストパス</t>
   </si>
   <si>
-    <t>{"timestamp":"2026-04-03T12:00:00","status":400,"error":"Bad Request","message":"タイトルを入力してください","path":"/api/tasks"}</t>
-  </si>
-  <si>
     <t>認証・認可エラー方針</t>
   </si>
   <si>
@@ -669,9 +558,6 @@
     <t>署名不正・形式不正・改ざんトークン</t>
   </si>
   <si>
-    <t>認証情報が不正です</t>
-  </si>
-  <si>
     <t>JWT期限切れ</t>
   </si>
   <si>
@@ -687,9 +573,6 @@
     <t>権限不足・操作対象へのアクセス権なし</t>
   </si>
   <si>
-    <t>この操作を実行する権限がありません</t>
-  </si>
-  <si>
     <t>フロントエンド制御前提</t>
   </si>
   <si>
@@ -711,9 +594,6 @@
     <t>/login</t>
   </si>
   <si>
-    <t>期限切れ・不正トークンを含む</t>
-  </si>
-  <si>
     <t>保護画面へ未認証アクセス</t>
   </si>
   <si>
@@ -732,9 +612,6 @@
     <t>現画面</t>
   </si>
   <si>
-    <t>自動ログアウトはしない</t>
-  </si>
-  <si>
     <t>POST /api/auth/register ユーザー登録</t>
   </si>
   <si>
@@ -747,9 +624,6 @@
     <t>成功ステータス</t>
   </si>
   <si>
-    <t>201想定</t>
-  </si>
-  <si>
     <t>リクエスト</t>
   </si>
   <si>
@@ -774,9 +648,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>パスワード（8文字以上）</t>
-  </si>
-  <si>
     <t>{"name":"佐伯将伍","email":"test@example.com","password":"password123"}</t>
   </si>
   <si>
@@ -834,9 +705,6 @@
     <t>password8文字未満</t>
   </si>
   <si>
-    <t>パスワードは8文字以上で入力してください</t>
-  </si>
-  <si>
     <t>業務エラー</t>
   </si>
   <si>
@@ -846,21 +714,12 @@
     <t>409</t>
   </si>
   <si>
-    <t>既に使用されているメールアドレスです</t>
-  </si>
-  <si>
     <t>POST /api/auth/login ログイン</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>フロント側でtoken保持</t>
-  </si>
-  <si>
-    <t>パスワード</t>
-  </si>
-  <si>
     <t>{"email":"test@example.com","password":"password123"}</t>
   </si>
   <si>
@@ -888,9 +747,6 @@
     <t>エラー</t>
   </si>
   <si>
-    <t>必須不足</t>
-  </si>
-  <si>
     <t>入力内容に誤りがあります</t>
   </si>
   <si>
@@ -903,54 +759,27 @@
     <t>401</t>
   </si>
   <si>
-    <t>メールアドレスまたはパスワードが正しくありません</t>
-  </si>
-  <si>
-    <t>JWT不正/期限切れは保護APIアクセス時に401を返却</t>
-  </si>
-  <si>
-    <t>詳細は「共通仕様」参照</t>
-  </si>
-  <si>
     <t>フロント制御</t>
   </si>
   <si>
-    <t>ログイン成功時はtoken保持後、直前画面へ復帰（なければ一覧）</t>
-  </si>
-  <si>
     <t>GET /api/tasks タスク一覧取得</t>
   </si>
   <si>
     <t>参照可能なタスク一覧を取得する</t>
   </si>
   <si>
-    <t>第1段階では作成者または担当者のタスクのみ返却。将来はチームADMIN参照対応</t>
-  </si>
-  <si>
     <t>クエリパラメータ</t>
   </si>
   <si>
-    <t>TODO / DOING / DONE（将来拡張）</t>
-  </si>
-  <si>
     <t>priority</t>
   </si>
   <si>
-    <t>LOW / MEDIUM / HIGH（将来拡張）</t>
-  </si>
-  <si>
     <t>assignedUserId</t>
   </si>
   <si>
-    <t>担当者ID（将来拡張）</t>
-  </si>
-  <si>
     <t>keyword</t>
   </si>
   <si>
-    <t>タイトル・説明検索（将来拡張）</t>
-  </si>
-  <si>
     <t>[].id</t>
   </si>
   <si>
@@ -1020,15 +849,9 @@
     <t>500</t>
   </si>
   <si>
-    <t>タスク一覧の取得に失敗しました</t>
-  </si>
-  <si>
     <t>GET /api/tasks/{taskId} タスク詳細取得</t>
   </si>
   <si>
-    <t>コメント・添付は別APIでも取得可</t>
-  </si>
-  <si>
     <t>title</t>
   </si>
   <si>
@@ -1068,9 +891,6 @@
     <t>404</t>
   </si>
   <si>
-    <t>対象タスクが見つかりません</t>
-  </si>
-  <si>
     <t>POST /api/tasks タスク作成</t>
   </si>
   <si>
@@ -1083,27 +903,12 @@
     <t>タイトル（100文字以内）</t>
   </si>
   <si>
-    <t>説明（任意）</t>
-  </si>
-  <si>
     <t>TODO / DOING / DONE</t>
   </si>
   <si>
     <t>期限（yyyy-MM-dd）</t>
   </si>
   <si>
-    <t>teamId</t>
-  </si>
-  <si>
-    <t>チームID（任意）</t>
-  </si>
-  <si>
-    <t>{"title":"API設計書を作成する","description":"認証APIとタスクAPIを整理する","status":"TODO","priority":"HIGH","dueDate":"2026-04-12","assignedUserId":1,"teamId":null}</t>
-  </si>
-  <si>
-    <t>{"id":2,"title":"API設計書を作成する","description":"認証APIとタスクAPIを整理する","status":"TODO","priority":"HIGH","dueDate":"2026-04-12","assignedUser":{"id":1,"name":"佐伯将伍"},"createdAt":"2026-04-03T11:00:00","updatedAt":"2026-04-03T11:00:00"}</t>
-  </si>
-  <si>
     <t>title未入力</t>
   </si>
   <si>
@@ -1116,12 +921,6 @@
     <t>PUT /api/tasks/{taskId} タスク更新</t>
   </si>
   <si>
-    <t>{"title":"API設計書を更新する","description":"レスポンス例とエラー設計を追加する","status":"DOING","priority":"HIGH","dueDate":"2026-04-13","assignedUserId":1,"teamId":null}</t>
-  </si>
-  <si>
-    <t>{"id":2,"title":"API設計書を更新する","description":"レスポンス例とエラー設計を追加する","status":"DOING","priority":"HIGH","dueDate":"2026-04-13","assignedUser":{"id":1,"name":"佐伯将伍"},"createdAt":"2026-04-03T11:00:00","updatedAt":"2026-04-03T12:00:00"}</t>
-  </si>
-  <si>
     <t>DELETE /api/tasks/{taskId} タスク削除</t>
   </si>
   <si>
@@ -1134,21 +933,12 @@
     <t>成功時レスポンスボディなし</t>
   </si>
   <si>
-    <t>将来拡張API</t>
-  </si>
-  <si>
     <t>実装優先度</t>
   </si>
   <si>
-    <t>タスク詳細のコメント欄</t>
-  </si>
-  <si>
     <t>中</t>
   </si>
   <si>
-    <t>本文必須</t>
-  </si>
-  <si>
     <t>メタ情報一覧</t>
   </si>
   <si>
@@ -1185,9 +975,6 @@
     <t>タスク作成画面 / タスク編集画面</t>
   </si>
   <si>
-    <t>担当者プルダウン表示用</t>
-  </si>
-  <si>
     <t>担当者ユーザーID（任意）。フォームでは GET /api/users の候補から選択</t>
   </si>
   <si>
@@ -1197,9 +984,6 @@
     <t>担当者プルダウン表示用の候補一覧を取得する</t>
   </si>
   <si>
-    <t>認証済みユーザーを候補として返却する</t>
-  </si>
-  <si>
     <t>なし</t>
   </si>
   <si>
@@ -1218,7 +1002,290 @@
     <t>[{"id":1,"name":"佐伯将伍","email":"test@example.com"},{"id":2,"name":"田中花子","email":"hanako@example.com"}]</t>
   </si>
   <si>
-    <t>担当者候補一覧の取得に失敗しました</t>
+    <t>現行実装API + 将来拡張候補</t>
+  </si>
+  <si>
+    <t>認証 / タスク / ユーザー候補 / 認証確認 / 監視</t>
+  </si>
+  <si>
+    <t>現行実装は認証、タスクCRUD、担当者候補取得、認証確認、ヘルスチェック</t>
+  </si>
+  <si>
+    <t>メールアドレスは一意。重複時は USR-001</t>
+  </si>
+  <si>
+    <t>成功時に JWT と user を返却</t>
+  </si>
+  <si>
+    <t>status / priority / assignedUserId / keyword に対応。現行フロントは取得後にクライアント側で絞り込み</t>
+  </si>
+  <si>
+    <t>作成者または担当者のみ参照可</t>
+  </si>
+  <si>
+    <t>assignedUserId は省略可。createdBy は認証ユーザー</t>
+  </si>
+  <si>
+    <t>作成者または担当者のみ更新可。assignedUserId を省略/null にすると担当者解除</t>
+  </si>
+  <si>
+    <t>作成者のみ削除可。成功時 204</t>
+  </si>
+  <si>
+    <t>認証確認</t>
+  </si>
+  <si>
+    <t>現在ユーザー取得</t>
+  </si>
+  <si>
+    <t>/api/auth-test/me</t>
+  </si>
+  <si>
+    <t>JWT から現在のユーザーIDとメールアドレスを返す</t>
+  </si>
+  <si>
+    <t>開発・疎通確認</t>
+  </si>
+  <si>
+    <t>認証フィルタ動作確認用</t>
+  </si>
+  <si>
+    <t>監視</t>
+  </si>
+  <si>
+    <t>ヘルスチェック</t>
+  </si>
+  <si>
+    <t>/actuator/health</t>
+  </si>
+  <si>
+    <t>アプリケーションの稼働状態を返す</t>
+  </si>
+  <si>
+    <t>運用監視</t>
+  </si>
+  <si>
+    <t>Spring Boot Actuator</t>
+  </si>
+  <si>
+    <t>name 昇順、同名時は id 昇順で返却</t>
+  </si>
+  <si>
+    <t>アプリAPI: /api、監視API: /actuator</t>
+  </si>
+  <si>
+    <t>コントローラ API は /api 配下、ヘルスチェックは /actuator/health</t>
+  </si>
+  <si>
+    <t>現行実装は JSON のみ（multipart/form-data は未実装）</t>
+  </si>
+  <si>
+    <t>createdAt / updatedAt は LocalDateTime、timestamp は OffsetDateTime</t>
+  </si>
+  <si>
+    <t>他人タスクの参照 / 更新 / 削除</t>
+  </si>
+  <si>
+    <t>taskId / assignedUserId が存在しない</t>
+  </si>
+  <si>
+    <t>2026-04-03T12:00:00+09:00</t>
+  </si>
+  <si>
+    <t>errorCode</t>
+  </si>
+  <si>
+    <t>アプリケーション内エラーコード</t>
+  </si>
+  <si>
+    <t>VAL-TASK-001</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>項目別詳細。バリデーション時のみ</t>
+  </si>
+  <si>
+    <t>[{"field":"title","message":"タイトルを入力してください"}]</t>
+  </si>
+  <si>
+    <t>{"timestamp":"2026-04-03T12:00:00+09:00","status":400,"errorCode":"VAL-TASK-001","message":"入力内容に誤りがあります","details":[{"field":"title","message":"タイトルを入力してください"}],"path":"/api/tasks","requestId":"550e8400-e29b-41d4-a716-446655440000"}</t>
+  </si>
+  <si>
+    <t>トークンが不正です</t>
+  </si>
+  <si>
+    <t>セッションの有効期限が切れています</t>
+  </si>
+  <si>
+    <t>操作権限がありません</t>
+  </si>
+  <si>
+    <t>期限切れ・不正トークン時は token を破棄し app:unauthorized を発火</t>
+  </si>
+  <si>
+    <t>エラー表示のみ。自動ログアウトはしない</t>
+  </si>
+  <si>
+    <t>パスワード（8文字以上100文字以下）</t>
+  </si>
+  <si>
+    <t>パスワードは8文字以上100文字以下で入力してください</t>
+  </si>
+  <si>
+    <t>メールアドレスは既に登録されています</t>
+  </si>
+  <si>
+    <t>フロント側で token を保持し、以後 Authorization ヘッダへ付与</t>
+  </si>
+  <si>
+    <t>必須不足 / 形式不正</t>
+  </si>
+  <si>
+    <t>認証に失敗しました</t>
+  </si>
+  <si>
+    <t>保護APIアクセス時の未認証 / JWT不正 / 期限切れ</t>
+  </si>
+  <si>
+    <t>AUTH-001 / AUTH-003 / AUTH-004 を返却</t>
+  </si>
+  <si>
+    <t>ログイン成功時は token 保持後、直前画面へ復帰（なければ /tasks）</t>
+  </si>
+  <si>
+    <t>作成者または担当者のタスクだけを返す。status / priority / assignedUserId / keyword による絞り込みに対応</t>
+  </si>
+  <si>
+    <t>TODO / DOING / DONE で絞り込み</t>
+  </si>
+  <si>
+    <t>LOW / MEDIUM / HIGH で絞り込み</t>
+  </si>
+  <si>
+    <t>担当者ユーザーIDで絞り込み</t>
+  </si>
+  <si>
+    <t>タイトルの部分一致検索</t>
+  </si>
+  <si>
+    <t>トークンが不正です / セッションの有効期限が切れています</t>
+  </si>
+  <si>
+    <t>DB障害 / 想定外例外</t>
+  </si>
+  <si>
+    <t>データの取得または更新に失敗しました / システムエラーが発生しました。しばらくしてから再度お試しください。</t>
+  </si>
+  <si>
+    <t>作成者または担当者のみ参照できる</t>
+  </si>
+  <si>
+    <t>タスク本文と関連ユーザー情報を返却</t>
+  </si>
+  <si>
+    <t>対象タスクの参照権限がありません</t>
+  </si>
+  <si>
+    <t>タスクが存在しません</t>
+  </si>
+  <si>
+    <t>説明（任意、5000文字以内）</t>
+  </si>
+  <si>
+    <t>LOW / MEDIUM / HIGH</t>
+  </si>
+  <si>
+    <t>担当者ユーザーID（任意）。null / 省略で未割当。GET /api/users の候補から選択</t>
+  </si>
+  <si>
+    <t>{"title":"API設計書を作成する","description":"認証APIとタスクAPIを整理する","status":"TODO","priority":"HIGH","dueDate":"2026-04-12","assignedUserId":1}</t>
+  </si>
+  <si>
+    <t>assignedUser</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>担当者情報（id, name）</t>
+  </si>
+  <si>
+    <t>createdBy</t>
+  </si>
+  <si>
+    <t>作成者情報（id, name）</t>
+  </si>
+  <si>
+    <t>常に返却</t>
+  </si>
+  <si>
+    <t>{"id":2,"title":"API設計書を作成する","description":"認証APIとタスクAPIを整理する","status":"TODO","priority":"HIGH","dueDate":"2026-04-12","assignedUser":{"id":1,"name":"佐伯将伍"},"createdBy":{"id":3,"name":"作成者ユーザー"},"createdAt":"2026-04-03T11:00:00","updatedAt":"2026-04-03T11:00:00"}</t>
+  </si>
+  <si>
+    <t>status不正 / dueDate形式不正 / priority不正</t>
+  </si>
+  <si>
+    <t>入力内容に誤りがあります（detailsに項目別メッセージ）</t>
+  </si>
+  <si>
+    <t>assignedUserId不存在</t>
+  </si>
+  <si>
+    <t>ユーザーが存在しません</t>
+  </si>
+  <si>
+    <t>{"title":"API設計書を更新する","description":"レスポンス例とエラー設計を追加する","status":"DOING","priority":"HIGH","dueDate":"2026-04-13","assignedUserId":1}</t>
+  </si>
+  <si>
+    <t>{"id":2,"title":"API設計書を更新する","description":"レスポンス例とエラー設計を追加する","status":"DOING","priority":"HIGH","dueDate":"2026-04-13","assignedUser":{"id":1,"name":"佐伯将伍"},"createdBy":{"id":3,"name":"作成者ユーザー"},"createdAt":"2026-04-03T11:00:00","updatedAt":"2026-04-03T12:00:00"}</t>
+  </si>
+  <si>
+    <t>title未入力 / status不正 / dueDate形式不正 など</t>
+  </si>
+  <si>
+    <t>作成者でも担当者でもないユーザーが更新</t>
+  </si>
+  <si>
+    <t>タスク更新権限がありません</t>
+  </si>
+  <si>
+    <t>taskId不存在 / assignedUserId不存在</t>
+  </si>
+  <si>
+    <t>タスクが存在しません / ユーザーが存在しません</t>
+  </si>
+  <si>
+    <t>タスク削除権限がありません</t>
+  </si>
+  <si>
+    <t>認証済みユーザーを name 昇順、同名時は id 昇順で返却する</t>
+  </si>
+  <si>
+    <t>補助API / 将来拡張API</t>
+  </si>
+  <si>
+    <t>補助</t>
+  </si>
+  <si>
+    <t>認証コンテキスト確認</t>
+  </si>
+  <si>
+    <t>userId / email を返却</t>
+  </si>
+  <si>
+    <t>実装済</t>
+  </si>
+  <si>
+    <t>Spring Boot Actuator の health</t>
+  </si>
+  <si>
+    <t>項目</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1264,7 +1331,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1284,11 +1351,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1392,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1406,14 +1468,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1439,21 +1498,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1756,7 +1809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1772,14 +1825,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -1826,719 +1879,371 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>38</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="F11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>51</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>36</v>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>56</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>360</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>67</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>68</v>
+        <v>315</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>69</v>
+        <v>316</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>317</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>72</v>
+        <v>318</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>55</v>
+        <v>319</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>73</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>70</v>
+        <v>323</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>72</v>
+        <v>324</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>55</v>
+        <v>325</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>68</v>
+        <v>291</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>72</v>
+        <v>294</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>55</v>
+        <v>295</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>366</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2560,17 +2265,17 @@
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="26" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2580,102 +2285,102 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>328</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>329</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
@@ -2683,13 +2388,13 @@
         <v>200</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
@@ -2697,13 +2402,13 @@
         <v>201</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
@@ -2711,13 +2416,13 @@
         <v>204</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
@@ -2725,13 +2430,13 @@
         <v>400</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -2739,13 +2444,13 @@
         <v>401</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
@@ -2753,13 +2458,13 @@
         <v>403</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>156</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -2767,13 +2472,13 @@
         <v>404</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>159</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
@@ -2781,13 +2486,13 @@
         <v>409</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
@@ -2795,268 +2500,282 @@
         <v>500</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
-      <c r="A21" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
+      <c r="A21" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>132</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>178</v>
+        <v>336</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>148</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>182</v>
+        <v>338</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>183</v>
+        <v>340</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="243" customHeight="1">
+      <c r="A29" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
-      <c r="A30" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
+      <c r="A30" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="A32" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" s="14">
         <v>401</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>191</v>
+      <c r="C32" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B33" s="15">
+      <c r="A33" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="14">
         <v>401</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>194</v>
+      <c r="C33" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="14">
         <v>401</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>197</v>
+      <c r="C34" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="A35" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="14">
         <v>403</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>200</v>
+      <c r="C35" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1">
-      <c r="A37" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
+      <c r="A37" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13"/>
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>208</v>
+      <c r="A39" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>211</v>
+      <c r="A40" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>215</v>
+      <c r="A41" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3085,19 +2804,19 @@
     <col min="7" max="26" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1">
+      <c r="A1" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>399</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -3117,285 +2836,285 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" thickBot="1">
+      <c r="A6" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>229</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
+      <c r="A11" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" thickBot="1">
+      <c r="A13" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
+      <c r="A19" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1">
+      <c r="A21" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>248</v>
+        <v>205</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>249</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" thickBot="1">
+      <c r="A29" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1">
       <c r="A30" s="1" t="s">
@@ -3419,259 +3138,259 @@
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F32" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1">
-      <c r="A34" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="19"/>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A34" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="22"/>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1">
-      <c r="A40" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="19"/>
+      <c r="A38" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A40" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="22"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="19"/>
+      <c r="A46" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A48" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="18"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>267</v>
+        <v>352</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>272</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="36" customHeight="1">
-      <c r="A52" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-    </row>
-    <row r="53" spans="1:6" ht="36" customHeight="1">
-      <c r="A53" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
+      <c r="A52" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+    </row>
+    <row r="53" spans="1:6" ht="79" customHeight="1">
+      <c r="A53" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3708,14 +3427,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16" thickBot="1">
-      <c r="A1" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
@@ -3739,334 +3458,326 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30">
       <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>279</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1"/>
     <row r="6" spans="1:6" ht="16" thickBot="1">
-      <c r="A6" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="A6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>281</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="3" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" s="3" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>285</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="3" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>287</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1"/>
     <row r="13" spans="1:6" ht="16" thickBot="1">
-      <c r="A13" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="A13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" s="3" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="3" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" s="3" t="s">
-        <v>293</v>
+        <v>236</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" s="3" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" s="3" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" s="3" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" s="3" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" s="3" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="22"/>
+      <c r="A23" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21"/>
     </row>
     <row r="24" spans="1:6" ht="15" thickBot="1"/>
     <row r="25" spans="1:6" ht="16" thickBot="1">
-      <c r="A25" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="A25" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-    </row>
-    <row r="29" spans="1:6" ht="15">
-      <c r="A29" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>311</v>
-      </c>
+      <c r="A28" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" spans="1:6" ht="30">
+      <c r="A29" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="23"/>
@@ -4078,14 +3789,14 @@
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1"/>
     <row r="33" spans="1:6" ht="16" thickBot="1">
-      <c r="A33" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="11"/>
+      <c r="A33" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="10"/>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" s="1" t="s">
@@ -4109,318 +3820,336 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30">
+      <c r="A36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" thickBot="1"/>
     <row r="38" spans="1:6" ht="16" thickBot="1">
-      <c r="A38" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="11"/>
+      <c r="A38" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" s="3" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" s="3" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" s="3" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" s="3" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" s="3" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="D47" s="3"/>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" s="3" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" s="3" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="22"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" s="3" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="22"/>
+      <c r="A52" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="21"/>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1"/>
     <row r="54" spans="1:6" ht="16" thickBot="1">
-      <c r="A54" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="11"/>
+      <c r="A54" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="10"/>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
-      <c r="A57" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
+      <c r="A57" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
     </row>
     <row r="58" spans="1:6" ht="15">
-      <c r="A58" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
+      <c r="A58" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1"/>
     <row r="62" spans="1:6" ht="16" thickBot="1">
-      <c r="A62" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="11"/>
+      <c r="A62" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="10"/>
     </row>
     <row r="63" spans="1:6" ht="15">
-      <c r="A63" s="26" t="s">
+      <c r="A63" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="22"/>
+      <c r="B63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E63" s="1" t="s">
         <v>1</v>
       </c>
@@ -4430,407 +4159,429 @@
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F65" s="3" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
-      <c r="A67" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="11"/>
+      <c r="A67" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="10"/>
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>331</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" s="3" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="22"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15">
+      <c r="A72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" s="3" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="22" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15">
-      <c r="A75" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>174</v>
-      </c>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15">
+      <c r="A74" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="3" t="s">
-        <v>336</v>
-      </c>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" spans="1:6" ht="90">
-      <c r="A76" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="10"/>
+      <c r="A76" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="9"/>
     </row>
     <row r="78" spans="1:6" ht="15">
-      <c r="A78" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="11"/>
+      <c r="A78" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="10"/>
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D80" s="3"/>
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="D81" s="3"/>
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D82" s="3"/>
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D83" s="3"/>
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" s="3" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="D84" s="3"/>
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" s="3" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="22"/>
-    </row>
-    <row r="87" spans="1:6" ht="15">
+        <v>240</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="30">
+      <c r="A86" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30">
       <c r="A87" s="3" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>171</v>
+        <v>374</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21"/>
-      <c r="D88" s="22"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15">
+      <c r="A88" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" s="3" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="135">
-      <c r="A90" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="10"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="150">
+      <c r="A90" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="9"/>
     </row>
     <row r="92" spans="1:6" ht="15">
-      <c r="A92" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="11"/>
+      <c r="A92" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="10"/>
     </row>
     <row r="93" spans="1:6" ht="15">
       <c r="A93" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15">
       <c r="A94" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>339</v>
+        <v>274</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15">
       <c r="A95" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>340</v>
+        <v>275</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="B96" s="21"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="22"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="30">
+      <c r="A96" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" spans="1:6" ht="15">
       <c r="A97" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15">
-      <c r="A98" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B98" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
+      <c r="A98" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
     </row>
     <row r="99" spans="1:6" ht="15">
-      <c r="A99" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B99" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16"/>
+      <c r="A99" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="E99" s="15"/>
+      <c r="F99" s="15"/>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="23"/>
@@ -4839,14 +4590,14 @@
       <c r="D101" s="23"/>
     </row>
     <row r="102" spans="1:6" ht="15">
-      <c r="A102" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="11"/>
+      <c r="A102" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="10"/>
     </row>
     <row r="103" spans="1:6" ht="15">
       <c r="A103" s="1" t="s">
@@ -4870,399 +4621,427 @@
     </row>
     <row r="104" spans="1:6" ht="15">
       <c r="A104" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15">
       <c r="A105" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F105" s="3" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15">
-      <c r="A107" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="11"/>
+      <c r="A107" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="10"/>
     </row>
     <row r="108" spans="1:6" ht="15">
       <c r="A108" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15">
       <c r="A109" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="B110" s="21"/>
-      <c r="C110" s="21"/>
-      <c r="D110" s="22"/>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15">
+      <c r="A110" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" s="8"/>
+      <c r="D110" s="3" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="15">
       <c r="A111" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="B112" s="21"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="22"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15">
+      <c r="A112" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="113" spans="1:4" ht="15">
       <c r="A113" s="3" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15">
       <c r="A114" s="3" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15">
-      <c r="A115" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>174</v>
-      </c>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="3" t="s">
-        <v>336</v>
-      </c>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" ht="90">
-      <c r="A116" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="10"/>
+      <c r="A116" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="9"/>
     </row>
     <row r="118" spans="1:4" ht="15">
-      <c r="A118" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="11"/>
+      <c r="A118" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="10"/>
     </row>
     <row r="119" spans="1:4" ht="15">
       <c r="A119" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15">
       <c r="A120" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D120" s="3"/>
     </row>
     <row r="121" spans="1:4" ht="15">
       <c r="A121" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:4" ht="15">
       <c r="A122" s="3" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" ht="15">
       <c r="A123" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="B124" s="21"/>
-      <c r="C124" s="21"/>
-      <c r="D124" s="22"/>
+    <row r="124" spans="1:4" ht="15">
+      <c r="A124" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D124" s="3"/>
     </row>
     <row r="125" spans="1:4" ht="15">
       <c r="A125" s="3" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D125" s="3"/>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="B126" s="21"/>
-      <c r="C126" s="21"/>
-      <c r="D126" s="22"/>
-    </row>
-    <row r="127" spans="1:4" ht="15">
+        <v>240</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="30">
+      <c r="A126" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="30">
       <c r="A127" s="3" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>171</v>
+        <v>374</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>300</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15">
       <c r="A128" s="3" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="15">
       <c r="A129" s="3" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="135">
-      <c r="A130" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="10"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="150">
+      <c r="A130" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="9"/>
     </row>
     <row r="131" spans="1:6" ht="15" thickBot="1"/>
     <row r="132" spans="1:6" ht="16" thickBot="1">
-      <c r="A132" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="11"/>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="B133" s="21"/>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="22"/>
-    </row>
-    <row r="134" spans="1:6" ht="15">
+      <c r="A132" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="10"/>
+    </row>
+    <row r="133" spans="1:6" ht="15">
+      <c r="A133" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" spans="1:6" ht="30">
       <c r="A134" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>149</v>
+        <v>386</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15">
       <c r="A135" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15">
-      <c r="A136" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B136" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C136" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D136" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16"/>
-    </row>
-    <row r="137" spans="1:6" ht="15">
-      <c r="A137" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B137" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" s="24" t="s">
+      <c r="A136" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B136" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="B138" s="21"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="22"/>
+      <c r="C136" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+    </row>
+    <row r="137" spans="1:6" ht="30">
+      <c r="A137" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="E137" s="15"/>
+      <c r="F137" s="15"/>
+    </row>
+    <row r="138" spans="1:6" ht="30">
+      <c r="A138" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="140" spans="1:6" ht="15" thickBot="1"/>
     <row r="141" spans="1:6" ht="16" thickBot="1">
-      <c r="A141" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="11"/>
+      <c r="A141" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="10"/>
     </row>
     <row r="142" spans="1:6" ht="15">
       <c r="A142" s="1" t="s">
@@ -5286,136 +5065,136 @@
     </row>
     <row r="143" spans="1:6" ht="15">
       <c r="A143" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="15">
       <c r="A144" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="F144" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="15">
+      <c r="A146" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="15">
-      <c r="A146" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="11"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="10"/>
     </row>
     <row r="147" spans="1:6" ht="15">
       <c r="A147" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="15">
       <c r="A148" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="15">
-      <c r="A149" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B149" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C149" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D149" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
+      <c r="A149" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B149" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C149" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D149" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E149" s="15"/>
+      <c r="F149" s="15"/>
     </row>
     <row r="150" spans="1:6" ht="15">
-      <c r="A150" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B150" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="C150" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E150" s="16"/>
-      <c r="F150" s="16"/>
+      <c r="A150" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D150" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="E150" s="15"/>
+      <c r="F150" s="15"/>
     </row>
     <row r="151" spans="1:6" ht="15">
       <c r="A151" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="15" thickBot="1"/>
     <row r="153" spans="1:6" ht="16" thickBot="1">
-      <c r="A153" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="B153" s="7"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="11"/>
+      <c r="A153" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B153" s="6"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="10"/>
     </row>
     <row r="154" spans="1:6" ht="15">
       <c r="A154" s="1" t="s">
@@ -5439,239 +5218,225 @@
     </row>
     <row r="155" spans="1:6" ht="15">
       <c r="A155" s="2" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="30">
       <c r="A156" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E156" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F156" s="3" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="15" thickBot="1"/>
     <row r="158" spans="1:6" ht="16" thickBot="1">
-      <c r="A158" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
+      <c r="A158" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B158" s="6"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
     </row>
     <row r="159" spans="1:6" ht="15">
       <c r="A159" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="B160" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="D160" s="24" t="s">
-        <v>373</v>
+      <c r="A160" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B160" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C160" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="D160" s="22" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="15" thickBot="1"/>
     <row r="162" spans="1:6" ht="16" thickBot="1">
-      <c r="A162" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
+      <c r="A162" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B162" s="6"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
     </row>
     <row r="163" spans="1:6" ht="15">
       <c r="A163" s="1" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="15">
       <c r="A164" s="3" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D164" s="3"/>
     </row>
     <row r="165" spans="1:6" ht="15">
       <c r="A165" s="3" t="s">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C165" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="15">
       <c r="A166" s="3" t="s">
-        <v>375</v>
+        <v>303</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D166" s="3"/>
     </row>
     <row r="167" spans="1:6">
-      <c r="A167" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="B167" s="21"/>
-      <c r="C167" s="21"/>
-      <c r="D167" s="22"/>
+      <c r="A167" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="B167" s="20"/>
+      <c r="C167" s="20"/>
+      <c r="D167" s="21"/>
     </row>
     <row r="168" spans="1:6" ht="15" thickBot="1"/>
     <row r="169" spans="1:6" ht="16" thickBot="1">
-      <c r="A169" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
+      <c r="A169" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B169" s="6"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="6"/>
     </row>
     <row r="170" spans="1:6" ht="15">
       <c r="A170" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="15">
       <c r="A171" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="15">
-      <c r="A172" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B172" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C172" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D172" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E172" s="16"/>
-      <c r="F172" s="16"/>
-    </row>
-    <row r="173" spans="1:6" ht="15">
+      <c r="A172" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B172" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D172" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E172" s="15"/>
+      <c r="F172" s="15"/>
+    </row>
+    <row r="173" spans="1:6" ht="30">
       <c r="A173" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>165</v>
+        <v>363</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="6">
     <mergeCell ref="A160:D160"/>
     <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A138:D138"/>
-    <mergeCell ref="A110:D110"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A133:F133"/>
-    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A124:D124"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A88:D88"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5681,405 +5446,404 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="71" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="26" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="1" spans="1:8" ht="15">
+      <c r="A1" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" ht="15">
       <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15">
+      <c r="A6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15">
+      <c r="A8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15">
+      <c r="A12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15">
+      <c r="A13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15">
+      <c r="A14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15">
+      <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15">
+      <c r="A16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="5" t="s">
-        <v>357</v>
+      <c r="H16" s="4" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
